--- a/output/pdf_financials_xlsx/STUD.xlsx
+++ b/output/pdf_financials_xlsx/STUD.xlsx
@@ -4493,40 +4493,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.145396</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.145396</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.145396</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.145396</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.845724</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.970314</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.517007</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.886173</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.147249</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.490531</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.639594</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.036789</v>
       </c>
     </row>
     <row r="93">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.253656</v>
+        <v>0.155076</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.03885</v>
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>5.182604</v>
+        <v>5.011841</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -5596,19 +5596,19 @@
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.563889</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>4.02</v>
+        <v>2.996535</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>5.363333</v>
+        <v>1.096096</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>17.667556</v>
+        <v>13.102578</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>2.622416</v>
+        <v>0.689437</v>
       </c>
     </row>
     <row r="119">
@@ -7860,7 +7860,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -7934,7 +7938,11 @@
           <t>Warrants reserve 13</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -9056,7 +9064,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -9130,7 +9142,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -9714,7 +9730,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -10086,7 +10106,11 @@
           <t>Warrants reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -10550,7 +10574,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -10620,7 +10648,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -11376,7 +11408,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.145396</v>
       </c>
@@ -13432,7 +13468,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -16794,7 +16834,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -18588,7 +18632,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>-0.09858</v>
       </c>
@@ -19336,7 +19384,11 @@
           <t>Prepaid deposit applied to exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -19844,7 +19896,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/STUD.xlsx
+++ b/output/pdf_financials_xlsx/STUD.xlsx
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.072362</v>
+        <v>0.407661</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0639</v>
+        <v>0.19924</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.070314</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.290032</v>
+        <v>0.304157</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.654267</v>
+        <v>1.406359</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.045626</v>
+        <v>0.122845</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.177526</v>
+        <v>0.585329</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.54267</v>
+        <v>0.959903</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.549823</v>
+        <v>0.91474</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.860219</v>
+        <v>2.302297</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>2.642213</v>
@@ -836,34 +836,34 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.072362</v>
+        <v>-0.407661</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.0639</v>
+        <v>-0.19924</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.070314</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.290032</v>
+        <v>-0.304157</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.654267</v>
+        <v>-1.406359</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.045626</v>
+        <v>-0.122845</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.177526</v>
+        <v>-0.585329</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.54267</v>
+        <v>-0.959903</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.549823</v>
+        <v>-0.91474</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.860219</v>
+        <v>-2.302297</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-2.642213</v>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.021096</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -900,16 +900,16 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.006657</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.034529</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.07757799999999999</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.056315</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>-0.304157</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.567867</v>
+        <v>-6.588963</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.122845</v>
@@ -1603,16 +1603,16 @@
         <v>-0.585329</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.614741</v>
+        <v>-0.621398</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.875923</v>
+        <v>-0.910452</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.224719</v>
+        <v>-2.302297</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-19.793286</v>
+        <v>-19.849601</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.99563</v>
@@ -1680,7 +1680,7 @@
         <v>-0.304157</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.567867</v>
+        <v>-6.588963</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.122845</v>
@@ -1689,16 +1689,16 @@
         <v>-0.585329</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.614741</v>
+        <v>-0.621398</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.875923</v>
+        <v>-0.910452</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.224719</v>
+        <v>-2.302297</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-19.793286</v>
+        <v>-19.849601</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.99563</v>
@@ -1895,25 +1895,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.151058</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000721</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.375522</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.307502</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001859</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.574675</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>3.198029</v>
@@ -1981,25 +1981,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.151058</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000721</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.375522</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.307502</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001859</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.574675</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.198029</v>
@@ -2509,13 +2509,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.307502</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001859</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.634675</v>
+        <v>0.06</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.019948</v>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
@@ -23904,7 +23904,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">

--- a/output/pdf_financials_xlsx/STUD.xlsx
+++ b/output/pdf_financials_xlsx/STUD.xlsx
@@ -14012,7 +14012,11 @@
           <t>Procceds from shares issued for cash</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
